--- a/artfynd/A 55086-2025 artfynd.xlsx
+++ b/artfynd/A 55086-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>130042644</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55086-2025 artfynd.xlsx
+++ b/artfynd/A 55086-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130042652</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>130042644</v>
       </c>
       <c r="B3" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
